--- a/Systeme electric/Товар в пути_SystemElectric на 22.09.2026.xlsx
+++ b/Systeme electric/Товар в пути_SystemElectric на 22.09.2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.0.13\од\Кейсы для Хакатона\Systeme electric\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\githack\hack-95b86b43-team\Systeme electric\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8979A244-FE36-4058-8234-1517686E9DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE5D993-6DD6-44D9-90F6-0CEED0D384BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9C436FAD-78C4-474E-84D2-F279FCB7E2F4}"/>
+    <workbookView xWindow="1044" yWindow="1044" windowWidth="17280" windowHeight="10500" xr2:uid="{9C436FAD-78C4-474E-84D2-F279FCB7E2F4}"/>
   </bookViews>
   <sheets>
     <sheet name="TDSheet" sheetId="1" r:id="rId1"/>
@@ -32,9 +32,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -4960,7 +4957,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5006,12 +5003,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5366,9 +5357,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -5392,7 +5380,7 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -5419,11 +5407,14 @@
     <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="12" fillId="11" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="12" fillId="10" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5433,7 +5424,37 @@
     <cellStyle name="Процентный" xfId="2" builtinId="5"/>
     <cellStyle name="Финансовый" xfId="1" builtinId="3"/>
   </cellStyles>
-  <dxfs count="43">
+  <dxfs count="23">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5634,236 +5655,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -5878,9 +5669,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5918,7 +5709,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6024,7 +5815,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6166,7 +5957,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6201,62 +5992,62 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:BR499"/>
-  <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="11.4" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.1640625" customWidth="1"/>
-    <col min="2" max="2" width="9.83203125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" style="8" customWidth="1"/>
     <col min="3" max="3" width="11" style="8" customWidth="1"/>
     <col min="4" max="4" width="82" style="8" customWidth="1"/>
-    <col min="5" max="5" width="5.5" style="49" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" style="8" customWidth="1" collapsed="1"/>
-    <col min="7" max="8" width="10.5" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="8.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="10.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="5.42578125" style="48" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="8" customWidth="1" collapsed="1"/>
+    <col min="7" max="8" width="10.42578125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="8.7109375" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="10.7109375" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="11" max="11" width="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="14" width="9.83203125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="18" width="11.83203125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="22" width="11.83203125" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="9.1640625" hidden="1" customWidth="1"/>
-    <col min="25" max="28" width="9.33203125" hidden="1" customWidth="1"/>
-    <col min="29" max="30" width="9.83203125" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="11.6640625" hidden="1" customWidth="1"/>
-    <col min="32" max="34" width="10.33203125" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="9.83203125" hidden="1" customWidth="1"/>
-    <col min="36" max="37" width="8.6640625" hidden="1" customWidth="1"/>
-    <col min="38" max="40" width="9.5" hidden="1" customWidth="1"/>
-    <col min="41" max="41" width="9.83203125" hidden="1" customWidth="1"/>
-    <col min="42" max="42" width="13.1640625" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="11.6640625" hidden="1" customWidth="1"/>
-    <col min="44" max="53" width="10.5" hidden="1" customWidth="1"/>
-    <col min="54" max="54" width="9.5" style="6" hidden="1" customWidth="1"/>
-    <col min="55" max="55" width="20.5" style="6" customWidth="1"/>
-    <col min="56" max="56" width="9.5" style="6" customWidth="1"/>
-    <col min="57" max="57" width="21.5" customWidth="1"/>
-    <col min="58" max="58" width="17.83203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="13.33203125" customWidth="1"/>
-    <col min="60" max="60" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="61" max="63" width="13.1640625" customWidth="1"/>
-    <col min="64" max="64" width="13.1640625" style="8" customWidth="1"/>
-    <col min="65" max="71" width="13.1640625" customWidth="1"/>
+    <col min="12" max="14" width="9.85546875" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="18" width="11.85546875" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="22" width="11.85546875" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="25" max="28" width="9.28515625" hidden="1" customWidth="1"/>
+    <col min="29" max="30" width="9.85546875" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="11.7109375" hidden="1" customWidth="1"/>
+    <col min="32" max="34" width="10.28515625" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="9.85546875" hidden="1" customWidth="1"/>
+    <col min="36" max="37" width="8.7109375" hidden="1" customWidth="1"/>
+    <col min="38" max="40" width="9.42578125" hidden="1" customWidth="1"/>
+    <col min="41" max="41" width="9.85546875" hidden="1" customWidth="1"/>
+    <col min="42" max="42" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="11.7109375" hidden="1" customWidth="1"/>
+    <col min="44" max="53" width="10.42578125" hidden="1" customWidth="1"/>
+    <col min="54" max="54" width="9.42578125" style="6" hidden="1" customWidth="1"/>
+    <col min="55" max="55" width="20.42578125" style="6" customWidth="1"/>
+    <col min="56" max="56" width="9.42578125" style="6" customWidth="1"/>
+    <col min="57" max="57" width="21.42578125" customWidth="1"/>
+    <col min="58" max="58" width="17.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="13.28515625" customWidth="1"/>
+    <col min="60" max="60" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="61" max="63" width="13.140625" customWidth="1"/>
+    <col min="64" max="64" width="13.140625" style="8" customWidth="1"/>
+    <col min="65" max="71" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" ht="11.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:60" ht="11.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
       <c r="E1" s="4"/>
       <c r="F1" s="5"/>
-      <c r="AT1" s="62" t="s">
+      <c r="AT1" s="61" t="s">
         <v>1547</v>
       </c>
-      <c r="AU1" s="62"/>
-      <c r="AV1" s="62"/>
-      <c r="AW1" s="62"/>
-      <c r="AX1" s="62"/>
-      <c r="AY1" s="62"/>
-      <c r="AZ1" s="62"/>
-      <c r="BA1" s="62"/>
-      <c r="BB1" s="62"/>
+      <c r="AU1" s="61"/>
+      <c r="AV1" s="61"/>
+      <c r="AW1" s="61"/>
+      <c r="AX1" s="61"/>
+      <c r="AY1" s="61"/>
+      <c r="AZ1" s="61"/>
+      <c r="BA1" s="61"/>
+      <c r="BB1" s="61"/>
       <c r="BE1" s="7"/>
       <c r="BG1" s="9"/>
     </row>
@@ -21832,7 +21623,7 @@
         <v>2.7961165048543686</v>
       </c>
       <c r="BB91" s="35"/>
-      <c r="BC91" s="42">
+      <c r="BC91" s="62">
         <v>40</v>
       </c>
       <c r="BD91" s="36"/>
@@ -34466,7 +34257,7 @@
       <c r="B165" s="27" t="s">
         <v>544</v>
       </c>
-      <c r="C165" s="43" t="s">
+      <c r="C165" s="42" t="s">
         <v>545</v>
       </c>
       <c r="D165" s="26" t="s">
@@ -34616,7 +34407,7 @@
       <c r="B166" s="27" t="s">
         <v>547</v>
       </c>
-      <c r="C166" s="43" t="s">
+      <c r="C166" s="42" t="s">
         <v>548</v>
       </c>
       <c r="D166" s="26" t="s">
@@ -34766,7 +34557,7 @@
       <c r="B167" s="27" t="s">
         <v>550</v>
       </c>
-      <c r="C167" s="43" t="s">
+      <c r="C167" s="42" t="s">
         <v>551</v>
       </c>
       <c r="D167" s="26" t="s">
@@ -35428,7 +35219,7 @@
       </c>
       <c r="BD170" s="36"/>
       <c r="BE170" s="37"/>
-      <c r="BH170" s="44"/>
+      <c r="BH170" s="43"/>
     </row>
     <row r="171" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="25">
@@ -35602,7 +35393,7 @@
         <v>0</v>
       </c>
       <c r="BD171" s="36"/>
-      <c r="BH171" s="44"/>
+      <c r="BH171" s="43"/>
     </row>
     <row r="172" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="38">
@@ -35776,7 +35567,7 @@
         <v>0</v>
       </c>
       <c r="BD172" s="36"/>
-      <c r="BH172" s="44"/>
+      <c r="BH172" s="43"/>
     </row>
     <row r="173" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="38">
@@ -35950,7 +35741,7 @@
         <v>0</v>
       </c>
       <c r="BD173" s="36"/>
-      <c r="BH173" s="44"/>
+      <c r="BH173" s="43"/>
     </row>
     <row r="174" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="25">
@@ -36125,7 +35916,7 @@
       </c>
       <c r="BD174" s="36"/>
       <c r="BE174" s="37"/>
-      <c r="BH174" s="44"/>
+      <c r="BH174" s="43"/>
     </row>
     <row r="175" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="38">
@@ -36299,7 +36090,7 @@
         <v>0</v>
       </c>
       <c r="BD175" s="36"/>
-      <c r="BH175" s="44"/>
+      <c r="BH175" s="43"/>
     </row>
     <row r="176" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="25">
@@ -36473,7 +36264,7 @@
         <v>0</v>
       </c>
       <c r="BD176" s="36"/>
-      <c r="BH176" s="44"/>
+      <c r="BH176" s="43"/>
     </row>
     <row r="177" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="38">
@@ -36647,7 +36438,7 @@
         <v>0</v>
       </c>
       <c r="BD177" s="36"/>
-      <c r="BH177" s="44"/>
+      <c r="BH177" s="43"/>
     </row>
     <row r="178" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="38">
@@ -36822,7 +36613,7 @@
       </c>
       <c r="BD178" s="36"/>
       <c r="BE178" s="37"/>
-      <c r="BH178" s="44"/>
+      <c r="BH178" s="43"/>
     </row>
     <row r="179" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="38">
@@ -36996,7 +36787,7 @@
         <v>0</v>
       </c>
       <c r="BD179" s="36"/>
-      <c r="BH179" s="44"/>
+      <c r="BH179" s="43"/>
     </row>
     <row r="180" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="25">
@@ -37171,7 +36962,7 @@
       </c>
       <c r="BD180" s="36"/>
       <c r="BE180" s="37"/>
-      <c r="BH180" s="44"/>
+      <c r="BH180" s="43"/>
     </row>
     <row r="181" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="38">
@@ -37345,7 +37136,7 @@
         <v>0</v>
       </c>
       <c r="BD181" s="36"/>
-      <c r="BH181" s="44"/>
+      <c r="BH181" s="43"/>
     </row>
     <row r="182" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="25">
@@ -37520,7 +37311,7 @@
       </c>
       <c r="BD182" s="36"/>
       <c r="BE182" s="37"/>
-      <c r="BH182" s="44"/>
+      <c r="BH182" s="43"/>
     </row>
     <row r="183" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="38">
@@ -37695,7 +37486,7 @@
       </c>
       <c r="BD183" s="36"/>
       <c r="BE183" s="37"/>
-      <c r="BH183" s="44"/>
+      <c r="BH183" s="43"/>
     </row>
     <row r="184" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="38">
@@ -37870,7 +37661,7 @@
       </c>
       <c r="BD184" s="36"/>
       <c r="BE184" s="41"/>
-      <c r="BH184" s="44"/>
+      <c r="BH184" s="43"/>
     </row>
     <row r="185" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="25">
@@ -38044,7 +37835,7 @@
         <v>0</v>
       </c>
       <c r="BD185" s="36"/>
-      <c r="BH185" s="44"/>
+      <c r="BH185" s="43"/>
     </row>
     <row r="186" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="38">
@@ -38219,7 +38010,7 @@
       </c>
       <c r="BD186" s="36"/>
       <c r="BE186" s="37"/>
-      <c r="BH186" s="44"/>
+      <c r="BH186" s="43"/>
     </row>
     <row r="187" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="25">
@@ -38393,7 +38184,7 @@
         <v>0</v>
       </c>
       <c r="BD187" s="36"/>
-      <c r="BH187" s="44"/>
+      <c r="BH187" s="43"/>
     </row>
     <row r="188" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="38">
@@ -38567,7 +38358,7 @@
         <v>0</v>
       </c>
       <c r="BD188" s="36"/>
-      <c r="BH188" s="44"/>
+      <c r="BH188" s="43"/>
     </row>
     <row r="189" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="38">
@@ -38741,7 +38532,7 @@
         <v>0</v>
       </c>
       <c r="BD189" s="36"/>
-      <c r="BH189" s="44"/>
+      <c r="BH189" s="43"/>
     </row>
     <row r="190" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="25">
@@ -38915,7 +38706,7 @@
         <v>0</v>
       </c>
       <c r="BD190" s="36"/>
-      <c r="BH190" s="44"/>
+      <c r="BH190" s="43"/>
     </row>
     <row r="191" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="38">
@@ -39090,7 +38881,7 @@
       </c>
       <c r="BD191" s="36"/>
       <c r="BE191" s="37"/>
-      <c r="BH191" s="44"/>
+      <c r="BH191" s="43"/>
     </row>
     <row r="192" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="25">
@@ -39264,7 +39055,7 @@
         <v>0</v>
       </c>
       <c r="BD192" s="36"/>
-      <c r="BH192" s="44"/>
+      <c r="BH192" s="43"/>
     </row>
     <row r="193" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="38">
@@ -39439,7 +39230,7 @@
       </c>
       <c r="BD193" s="36"/>
       <c r="BE193" s="41"/>
-      <c r="BH193" s="44"/>
+      <c r="BH193" s="43"/>
     </row>
     <row r="194" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="38">
@@ -39613,7 +39404,7 @@
         <v>0</v>
       </c>
       <c r="BD194" s="36"/>
-      <c r="BH194" s="44"/>
+      <c r="BH194" s="43"/>
     </row>
     <row r="195" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="38">
@@ -39788,7 +39579,7 @@
       </c>
       <c r="BD195" s="36"/>
       <c r="BE195" s="37"/>
-      <c r="BH195" s="44"/>
+      <c r="BH195" s="43"/>
     </row>
     <row r="196" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="25">
@@ -39963,7 +39754,7 @@
       </c>
       <c r="BD196" s="36"/>
       <c r="BE196" s="37"/>
-      <c r="BH196" s="44"/>
+      <c r="BH196" s="43"/>
     </row>
     <row r="197" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="38">
@@ -40137,7 +39928,7 @@
         <v>0</v>
       </c>
       <c r="BD197" s="36"/>
-      <c r="BH197" s="44"/>
+      <c r="BH197" s="43"/>
     </row>
     <row r="198" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="25">
@@ -40311,7 +40102,7 @@
         <v>0</v>
       </c>
       <c r="BD198" s="36"/>
-      <c r="BH198" s="44"/>
+      <c r="BH198" s="43"/>
     </row>
     <row r="199" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="38">
@@ -40485,7 +40276,7 @@
         <v>0</v>
       </c>
       <c r="BD199" s="36"/>
-      <c r="BH199" s="44"/>
+      <c r="BH199" s="43"/>
     </row>
     <row r="200" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="38">
@@ -40660,7 +40451,7 @@
       </c>
       <c r="BD200" s="36"/>
       <c r="BE200" s="41"/>
-      <c r="BH200" s="44"/>
+      <c r="BH200" s="43"/>
     </row>
     <row r="201" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="25">
@@ -40826,7 +40617,7 @@
         <v>0</v>
       </c>
       <c r="BD201" s="36"/>
-      <c r="BH201" s="44"/>
+      <c r="BH201" s="43"/>
     </row>
     <row r="202" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="38">
@@ -41000,7 +40791,7 @@
         <v>0</v>
       </c>
       <c r="BD202" s="36"/>
-      <c r="BH202" s="44"/>
+      <c r="BH202" s="43"/>
     </row>
     <row r="203" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="25">
@@ -41174,7 +40965,7 @@
         <v>0</v>
       </c>
       <c r="BD203" s="36"/>
-      <c r="BH203" s="44"/>
+      <c r="BH203" s="43"/>
     </row>
     <row r="204" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="38">
@@ -41348,7 +41139,7 @@
         <v>0</v>
       </c>
       <c r="BD204" s="36"/>
-      <c r="BH204" s="44"/>
+      <c r="BH204" s="43"/>
     </row>
     <row r="205" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="38">
@@ -41522,7 +41313,7 @@
         <v>0</v>
       </c>
       <c r="BD205" s="36"/>
-      <c r="BH205" s="44"/>
+      <c r="BH205" s="43"/>
     </row>
     <row r="206" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="25">
@@ -41697,7 +41488,7 @@
       </c>
       <c r="BD206" s="36"/>
       <c r="BE206" s="37"/>
-      <c r="BH206" s="44"/>
+      <c r="BH206" s="43"/>
     </row>
     <row r="207" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="38">
@@ -41871,7 +41662,7 @@
         <v>0</v>
       </c>
       <c r="BD207" s="36"/>
-      <c r="BH207" s="44"/>
+      <c r="BH207" s="43"/>
     </row>
     <row r="208" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="25">
@@ -42037,7 +41828,7 @@
         <v>0</v>
       </c>
       <c r="BD208" s="36"/>
-      <c r="BH208" s="44"/>
+      <c r="BH208" s="43"/>
     </row>
     <row r="209" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="38">
@@ -42188,7 +41979,7 @@
       </c>
       <c r="BD209" s="36"/>
       <c r="BE209" s="37"/>
-      <c r="BH209" s="44"/>
+      <c r="BH209" s="43"/>
     </row>
     <row r="210" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="38">
@@ -42339,7 +42130,7 @@
       </c>
       <c r="BD210" s="36"/>
       <c r="BE210" s="37"/>
-      <c r="BH210" s="44"/>
+      <c r="BH210" s="43"/>
     </row>
     <row r="211" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="38">
@@ -42490,7 +42281,7 @@
       </c>
       <c r="BD211" s="36"/>
       <c r="BE211" s="37"/>
-      <c r="BH211" s="44"/>
+      <c r="BH211" s="43"/>
     </row>
     <row r="212" spans="1:60" s="8" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="25">
@@ -51359,7 +51150,7 @@
         <v>0</v>
       </c>
       <c r="BD263" s="36"/>
-      <c r="BE263" s="45"/>
+      <c r="BE263" s="44"/>
       <c r="BH263" s="37"/>
       <c r="BI263" s="37"/>
       <c r="BJ263" s="37"/>
@@ -51529,7 +51320,7 @@
         <v>0</v>
       </c>
       <c r="BD264" s="36"/>
-      <c r="BE264" s="45"/>
+      <c r="BE264" s="44"/>
       <c r="BH264" s="37"/>
       <c r="BI264" s="37"/>
       <c r="BJ264" s="37"/>
@@ -51699,7 +51490,7 @@
         <v>0</v>
       </c>
       <c r="BD265" s="36"/>
-      <c r="BE265" s="45"/>
+      <c r="BE265" s="44"/>
       <c r="BH265" s="37"/>
       <c r="BI265" s="37"/>
       <c r="BJ265" s="37"/>
@@ -51869,7 +51660,7 @@
         <v>0</v>
       </c>
       <c r="BD266" s="36"/>
-      <c r="BE266" s="45"/>
+      <c r="BE266" s="44"/>
       <c r="BH266" s="37"/>
       <c r="BI266" s="37"/>
       <c r="BJ266" s="37"/>
@@ -52039,7 +51830,7 @@
         <v>0</v>
       </c>
       <c r="BD267" s="36"/>
-      <c r="BE267" s="45"/>
+      <c r="BE267" s="44"/>
       <c r="BH267" s="37"/>
       <c r="BI267" s="37"/>
       <c r="BJ267" s="37"/>
@@ -52209,7 +52000,7 @@
         <v>0</v>
       </c>
       <c r="BD268" s="36"/>
-      <c r="BE268" s="45"/>
+      <c r="BE268" s="44"/>
       <c r="BH268" s="37"/>
       <c r="BI268" s="37"/>
       <c r="BJ268" s="37"/>
@@ -52379,7 +52170,7 @@
         <v>0</v>
       </c>
       <c r="BD269" s="36"/>
-      <c r="BE269" s="45"/>
+      <c r="BE269" s="44"/>
       <c r="BH269" s="37"/>
       <c r="BI269" s="37"/>
       <c r="BJ269" s="37"/>
@@ -52719,7 +52510,7 @@
         <v>0</v>
       </c>
       <c r="BD271" s="36"/>
-      <c r="BE271" s="45"/>
+      <c r="BE271" s="44"/>
       <c r="BH271" s="37"/>
       <c r="BI271" s="37"/>
       <c r="BJ271" s="37"/>
@@ -52889,7 +52680,7 @@
         <v>0</v>
       </c>
       <c r="BD272" s="36"/>
-      <c r="BE272" s="45"/>
+      <c r="BE272" s="44"/>
       <c r="BH272" s="37"/>
       <c r="BI272" s="37"/>
       <c r="BJ272" s="37"/>
@@ -53059,7 +52850,7 @@
         <v>0</v>
       </c>
       <c r="BD273" s="36"/>
-      <c r="BE273" s="45"/>
+      <c r="BE273" s="44"/>
       <c r="BH273" s="37"/>
       <c r="BI273" s="37"/>
       <c r="BJ273" s="37"/>
@@ -53229,7 +53020,7 @@
         <v>0</v>
       </c>
       <c r="BD274" s="36"/>
-      <c r="BE274" s="45"/>
+      <c r="BE274" s="44"/>
       <c r="BH274" s="37"/>
       <c r="BI274" s="37"/>
       <c r="BJ274" s="37"/>
@@ -53399,7 +53190,7 @@
         <v>0</v>
       </c>
       <c r="BD275" s="36"/>
-      <c r="BE275" s="45"/>
+      <c r="BE275" s="44"/>
       <c r="BH275" s="37"/>
       <c r="BI275" s="37"/>
       <c r="BJ275" s="37"/>
@@ -53569,7 +53360,7 @@
         <v>0</v>
       </c>
       <c r="BD276" s="36"/>
-      <c r="BE276" s="45"/>
+      <c r="BE276" s="44"/>
       <c r="BH276" s="37"/>
       <c r="BI276" s="37"/>
       <c r="BJ276" s="37"/>
@@ -53739,7 +53530,7 @@
         <v>0</v>
       </c>
       <c r="BD277" s="36"/>
-      <c r="BE277" s="45"/>
+      <c r="BE277" s="44"/>
       <c r="BH277" s="37"/>
       <c r="BI277" s="37"/>
       <c r="BJ277" s="37"/>
@@ -53909,7 +53700,7 @@
         <v>0</v>
       </c>
       <c r="BD278" s="36"/>
-      <c r="BE278" s="45"/>
+      <c r="BE278" s="44"/>
       <c r="BH278" s="37"/>
       <c r="BI278" s="37"/>
       <c r="BJ278" s="37"/>
@@ -54079,7 +53870,7 @@
         <v>0</v>
       </c>
       <c r="BD279" s="36"/>
-      <c r="BE279" s="45"/>
+      <c r="BE279" s="44"/>
       <c r="BH279" s="37"/>
       <c r="BI279" s="37"/>
       <c r="BJ279" s="37"/>
@@ -54249,7 +54040,7 @@
         <v>0</v>
       </c>
       <c r="BD280" s="36"/>
-      <c r="BE280" s="45"/>
+      <c r="BE280" s="44"/>
       <c r="BH280" s="37"/>
       <c r="BI280" s="37"/>
       <c r="BJ280" s="37"/>
@@ -54419,7 +54210,7 @@
         <v>0</v>
       </c>
       <c r="BD281" s="36"/>
-      <c r="BE281" s="45"/>
+      <c r="BE281" s="44"/>
       <c r="BH281" s="37"/>
       <c r="BI281" s="37"/>
       <c r="BJ281" s="37"/>
@@ -54589,7 +54380,7 @@
         <v>0</v>
       </c>
       <c r="BD282" s="36"/>
-      <c r="BE282" s="45"/>
+      <c r="BE282" s="44"/>
       <c r="BH282" s="37"/>
       <c r="BI282" s="37"/>
       <c r="BJ282" s="37"/>
@@ -54759,7 +54550,7 @@
         <v>0</v>
       </c>
       <c r="BD283" s="36"/>
-      <c r="BE283" s="45"/>
+      <c r="BE283" s="44"/>
       <c r="BH283" s="37"/>
       <c r="BI283" s="37"/>
       <c r="BJ283" s="37"/>
@@ -54929,7 +54720,7 @@
         <v>0</v>
       </c>
       <c r="BD284" s="36"/>
-      <c r="BE284" s="45"/>
+      <c r="BE284" s="44"/>
       <c r="BH284" s="37"/>
       <c r="BI284" s="37"/>
       <c r="BJ284" s="37"/>
@@ -55099,7 +54890,7 @@
         <v>0</v>
       </c>
       <c r="BD285" s="36"/>
-      <c r="BE285" s="45"/>
+      <c r="BE285" s="44"/>
       <c r="BH285" s="37"/>
       <c r="BI285" s="37"/>
       <c r="BJ285" s="37"/>
@@ -55269,7 +55060,7 @@
         <v>0</v>
       </c>
       <c r="BD286" s="36"/>
-      <c r="BE286" s="45"/>
+      <c r="BE286" s="44"/>
       <c r="BH286" s="37"/>
       <c r="BI286" s="37"/>
       <c r="BJ286" s="37"/>
@@ -55439,7 +55230,7 @@
         <v>0</v>
       </c>
       <c r="BD287" s="36"/>
-      <c r="BE287" s="45"/>
+      <c r="BE287" s="44"/>
       <c r="BH287" s="37"/>
       <c r="BI287" s="37"/>
       <c r="BJ287" s="37"/>
@@ -56459,7 +56250,7 @@
         <v>0</v>
       </c>
       <c r="BD293" s="36"/>
-      <c r="BE293" s="45"/>
+      <c r="BE293" s="44"/>
       <c r="BH293" s="37"/>
       <c r="BI293" s="37"/>
       <c r="BJ293" s="37"/>
@@ -56799,7 +56590,7 @@
         <v>0</v>
       </c>
       <c r="BD295" s="36"/>
-      <c r="BE295" s="45"/>
+      <c r="BE295" s="44"/>
       <c r="BH295" s="37"/>
       <c r="BI295" s="37"/>
       <c r="BJ295" s="37"/>
@@ -57479,7 +57270,7 @@
         <v>0</v>
       </c>
       <c r="BD299" s="36"/>
-      <c r="BE299" s="45"/>
+      <c r="BE299" s="44"/>
       <c r="BH299" s="37"/>
       <c r="BI299" s="37"/>
       <c r="BJ299" s="37"/>
@@ -58329,7 +58120,7 @@
         <v>0</v>
       </c>
       <c r="BD304" s="36"/>
-      <c r="BE304" s="45"/>
+      <c r="BE304" s="44"/>
       <c r="BH304" s="37"/>
       <c r="BI304" s="37"/>
       <c r="BJ304" s="37"/>
@@ -58839,7 +58630,7 @@
         <v>0</v>
       </c>
       <c r="BD307" s="36"/>
-      <c r="BE307" s="45"/>
+      <c r="BE307" s="44"/>
       <c r="BH307" s="37"/>
       <c r="BI307" s="37"/>
       <c r="BJ307" s="37"/>
@@ -59009,7 +58800,7 @@
         <v>0</v>
       </c>
       <c r="BD308" s="36"/>
-      <c r="BE308" s="45"/>
+      <c r="BE308" s="44"/>
       <c r="BH308" s="37"/>
       <c r="BI308" s="37"/>
       <c r="BJ308" s="37"/>
@@ -59179,7 +58970,7 @@
         <v>0</v>
       </c>
       <c r="BD309" s="36"/>
-      <c r="BE309" s="45"/>
+      <c r="BE309" s="44"/>
       <c r="BH309" s="37"/>
       <c r="BI309" s="37"/>
       <c r="BJ309" s="37"/>
@@ -59349,7 +59140,7 @@
         <v>0</v>
       </c>
       <c r="BD310" s="36"/>
-      <c r="BE310" s="45"/>
+      <c r="BE310" s="44"/>
       <c r="BH310" s="37"/>
       <c r="BI310" s="37"/>
       <c r="BJ310" s="37"/>
@@ -59519,7 +59310,7 @@
         <v>0</v>
       </c>
       <c r="BD311" s="36"/>
-      <c r="BE311" s="45"/>
+      <c r="BE311" s="44"/>
       <c r="BH311" s="37"/>
       <c r="BI311" s="37"/>
       <c r="BJ311" s="37"/>
@@ -59689,7 +59480,7 @@
         <v>0</v>
       </c>
       <c r="BD312" s="36"/>
-      <c r="BE312" s="45"/>
+      <c r="BE312" s="44"/>
       <c r="BH312" s="37"/>
       <c r="BI312" s="37"/>
       <c r="BJ312" s="37"/>
@@ -59859,7 +59650,7 @@
         <v>0</v>
       </c>
       <c r="BD313" s="36"/>
-      <c r="BE313" s="45"/>
+      <c r="BE313" s="44"/>
       <c r="BH313" s="37"/>
       <c r="BI313" s="37"/>
       <c r="BJ313" s="37"/>
@@ -60029,7 +59820,7 @@
         <v>0</v>
       </c>
       <c r="BD314" s="36"/>
-      <c r="BE314" s="45"/>
+      <c r="BE314" s="44"/>
       <c r="BH314" s="37"/>
       <c r="BI314" s="37"/>
       <c r="BJ314" s="37"/>
@@ -60199,7 +59990,7 @@
         <v>0</v>
       </c>
       <c r="BD315" s="36"/>
-      <c r="BE315" s="45"/>
+      <c r="BE315" s="44"/>
       <c r="BH315" s="37"/>
       <c r="BI315" s="37"/>
       <c r="BJ315" s="37"/>
@@ -60369,7 +60160,7 @@
         <v>0</v>
       </c>
       <c r="BD316" s="36"/>
-      <c r="BE316" s="45"/>
+      <c r="BE316" s="44"/>
       <c r="BH316" s="37"/>
       <c r="BI316" s="37"/>
       <c r="BJ316" s="37"/>
@@ -60539,7 +60330,7 @@
         <v>0</v>
       </c>
       <c r="BD317" s="36"/>
-      <c r="BE317" s="45"/>
+      <c r="BE317" s="44"/>
       <c r="BH317" s="37"/>
       <c r="BI317" s="37"/>
       <c r="BJ317" s="37"/>
@@ -60709,7 +60500,7 @@
         <v>0</v>
       </c>
       <c r="BD318" s="36"/>
-      <c r="BE318" s="45"/>
+      <c r="BE318" s="44"/>
       <c r="BH318" s="37"/>
       <c r="BI318" s="37"/>
       <c r="BJ318" s="37"/>
@@ -60879,7 +60670,7 @@
         <v>0</v>
       </c>
       <c r="BD319" s="36"/>
-      <c r="BE319" s="45"/>
+      <c r="BE319" s="44"/>
       <c r="BH319" s="37"/>
       <c r="BI319" s="37"/>
       <c r="BJ319" s="37"/>
@@ -61219,7 +61010,7 @@
         <v>0</v>
       </c>
       <c r="BD321" s="36"/>
-      <c r="BE321" s="45"/>
+      <c r="BE321" s="44"/>
       <c r="BH321" s="37"/>
       <c r="BI321" s="37"/>
       <c r="BJ321" s="37"/>
@@ -61389,7 +61180,7 @@
         <v>0</v>
       </c>
       <c r="BD322" s="36"/>
-      <c r="BE322" s="45"/>
+      <c r="BE322" s="44"/>
       <c r="BH322" s="37"/>
       <c r="BI322" s="37"/>
       <c r="BJ322" s="37"/>
@@ -61559,7 +61350,7 @@
         <v>0</v>
       </c>
       <c r="BD323" s="36"/>
-      <c r="BE323" s="45"/>
+      <c r="BE323" s="44"/>
       <c r="BH323" s="37"/>
       <c r="BI323" s="37"/>
       <c r="BJ323" s="37"/>
@@ -61729,7 +61520,7 @@
         <v>0</v>
       </c>
       <c r="BD324" s="36"/>
-      <c r="BE324" s="45"/>
+      <c r="BE324" s="44"/>
       <c r="BH324" s="37"/>
       <c r="BI324" s="37"/>
       <c r="BJ324" s="37"/>
@@ -61899,7 +61690,7 @@
         <v>0</v>
       </c>
       <c r="BD325" s="36"/>
-      <c r="BE325" s="45"/>
+      <c r="BE325" s="44"/>
       <c r="BH325" s="37"/>
       <c r="BI325" s="37"/>
       <c r="BJ325" s="37"/>
@@ -62069,7 +61860,7 @@
         <v>0</v>
       </c>
       <c r="BD326" s="36"/>
-      <c r="BE326" s="45"/>
+      <c r="BE326" s="44"/>
       <c r="BH326" s="37"/>
       <c r="BI326" s="37"/>
       <c r="BJ326" s="37"/>
@@ -62239,7 +62030,7 @@
         <v>0</v>
       </c>
       <c r="BD327" s="36"/>
-      <c r="BE327" s="45"/>
+      <c r="BE327" s="44"/>
       <c r="BH327" s="37"/>
       <c r="BI327" s="37"/>
       <c r="BJ327" s="37"/>
@@ -62409,7 +62200,7 @@
         <v>0</v>
       </c>
       <c r="BD328" s="36"/>
-      <c r="BE328" s="45"/>
+      <c r="BE328" s="44"/>
       <c r="BH328" s="37"/>
       <c r="BI328" s="37"/>
       <c r="BJ328" s="37"/>
@@ -62749,7 +62540,7 @@
         <v>0</v>
       </c>
       <c r="BD330" s="36"/>
-      <c r="BE330" s="45"/>
+      <c r="BE330" s="44"/>
       <c r="BH330" s="37"/>
       <c r="BI330" s="37"/>
       <c r="BJ330" s="37"/>
@@ -62919,7 +62710,7 @@
         <v>0</v>
       </c>
       <c r="BD331" s="36"/>
-      <c r="BE331" s="45"/>
+      <c r="BE331" s="44"/>
       <c r="BH331" s="37"/>
       <c r="BI331" s="37"/>
       <c r="BJ331" s="37"/>
@@ -63089,7 +62880,7 @@
         <v>0</v>
       </c>
       <c r="BD332" s="36"/>
-      <c r="BE332" s="45"/>
+      <c r="BE332" s="44"/>
       <c r="BH332" s="37"/>
       <c r="BI332" s="37"/>
       <c r="BJ332" s="37"/>
@@ -63259,7 +63050,7 @@
         <v>0</v>
       </c>
       <c r="BD333" s="36"/>
-      <c r="BE333" s="45"/>
+      <c r="BE333" s="44"/>
       <c r="BH333" s="37"/>
       <c r="BI333" s="37"/>
       <c r="BJ333" s="37"/>
@@ -63429,7 +63220,7 @@
         <v>0</v>
       </c>
       <c r="BD334" s="36"/>
-      <c r="BE334" s="45"/>
+      <c r="BE334" s="44"/>
       <c r="BH334" s="37"/>
       <c r="BI334" s="37"/>
       <c r="BJ334" s="37"/>
@@ -63599,7 +63390,7 @@
         <v>0</v>
       </c>
       <c r="BD335" s="36"/>
-      <c r="BE335" s="45"/>
+      <c r="BE335" s="44"/>
       <c r="BH335" s="37"/>
       <c r="BI335" s="37"/>
       <c r="BJ335" s="37"/>
@@ -63769,7 +63560,7 @@
         <v>0</v>
       </c>
       <c r="BD336" s="36"/>
-      <c r="BE336" s="45"/>
+      <c r="BE336" s="44"/>
       <c r="BH336" s="37"/>
       <c r="BI336" s="37"/>
       <c r="BJ336" s="37"/>
@@ -63939,7 +63730,7 @@
         <v>0</v>
       </c>
       <c r="BD337" s="36"/>
-      <c r="BE337" s="45"/>
+      <c r="BE337" s="44"/>
       <c r="BH337" s="37"/>
       <c r="BI337" s="37"/>
       <c r="BJ337" s="37"/>
@@ -64109,7 +63900,7 @@
         <v>0</v>
       </c>
       <c r="BD338" s="36"/>
-      <c r="BE338" s="45"/>
+      <c r="BE338" s="44"/>
       <c r="BH338" s="37"/>
       <c r="BI338" s="37"/>
       <c r="BJ338" s="37"/>
@@ -64619,7 +64410,7 @@
         <v>0</v>
       </c>
       <c r="BD341" s="36"/>
-      <c r="BE341" s="45"/>
+      <c r="BE341" s="44"/>
       <c r="BH341" s="37"/>
       <c r="BI341" s="37"/>
       <c r="BJ341" s="37"/>
@@ -64959,7 +64750,7 @@
         <v>0</v>
       </c>
       <c r="BD343" s="36"/>
-      <c r="BE343" s="45"/>
+      <c r="BE343" s="44"/>
       <c r="BH343" s="37"/>
       <c r="BI343" s="37"/>
       <c r="BJ343" s="37"/>
@@ -65469,7 +65260,7 @@
         <v>0</v>
       </c>
       <c r="BD346" s="36"/>
-      <c r="BE346" s="45"/>
+      <c r="BE346" s="44"/>
       <c r="BH346" s="37"/>
       <c r="BI346" s="37"/>
       <c r="BJ346" s="37"/>
@@ -65639,7 +65430,7 @@
         <v>0</v>
       </c>
       <c r="BD347" s="36"/>
-      <c r="BE347" s="45"/>
+      <c r="BE347" s="44"/>
       <c r="BH347" s="37"/>
       <c r="BI347" s="37"/>
       <c r="BJ347" s="37"/>
@@ -65979,7 +65770,7 @@
         <v>0</v>
       </c>
       <c r="BD349" s="36"/>
-      <c r="BE349" s="45"/>
+      <c r="BE349" s="44"/>
       <c r="BH349" s="37"/>
       <c r="BI349" s="37"/>
       <c r="BJ349" s="37"/>
@@ -66149,7 +65940,7 @@
         <v>0</v>
       </c>
       <c r="BD350" s="36"/>
-      <c r="BE350" s="45"/>
+      <c r="BE350" s="44"/>
       <c r="BH350" s="37"/>
       <c r="BI350" s="37"/>
       <c r="BJ350" s="37"/>
@@ -66829,7 +66620,7 @@
         <v>0</v>
       </c>
       <c r="BD354" s="36"/>
-      <c r="BE354" s="45"/>
+      <c r="BE354" s="44"/>
       <c r="BH354" s="37"/>
       <c r="BI354" s="37"/>
       <c r="BJ354" s="37"/>
@@ -66999,7 +66790,7 @@
         <v>0</v>
       </c>
       <c r="BD355" s="36"/>
-      <c r="BE355" s="45"/>
+      <c r="BE355" s="44"/>
       <c r="BH355" s="37"/>
       <c r="BI355" s="37"/>
       <c r="BJ355" s="37"/>
@@ -67329,7 +67120,7 @@
         <v>0</v>
       </c>
       <c r="BD357" s="36"/>
-      <c r="BE357" s="45"/>
+      <c r="BE357" s="44"/>
       <c r="BH357" s="37"/>
       <c r="BI357" s="37"/>
       <c r="BJ357" s="37"/>
@@ -67499,7 +67290,7 @@
         <v>0</v>
       </c>
       <c r="BD358" s="36"/>
-      <c r="BE358" s="45"/>
+      <c r="BE358" s="44"/>
       <c r="BH358" s="37"/>
       <c r="BI358" s="37"/>
       <c r="BJ358" s="37"/>
@@ -67669,7 +67460,7 @@
         <v>0</v>
       </c>
       <c r="BD359" s="36"/>
-      <c r="BE359" s="45"/>
+      <c r="BE359" s="44"/>
       <c r="BH359" s="37"/>
       <c r="BI359" s="37"/>
       <c r="BJ359" s="37"/>
@@ -67839,7 +67630,7 @@
         <v>0</v>
       </c>
       <c r="BD360" s="36"/>
-      <c r="BE360" s="45"/>
+      <c r="BE360" s="44"/>
       <c r="BH360" s="37"/>
       <c r="BI360" s="37"/>
       <c r="BJ360" s="37"/>
@@ -68179,7 +67970,7 @@
         <v>0</v>
       </c>
       <c r="BD362" s="36"/>
-      <c r="BE362" s="45"/>
+      <c r="BE362" s="44"/>
       <c r="BH362" s="37"/>
       <c r="BI362" s="37"/>
       <c r="BJ362" s="37"/>
@@ -68349,7 +68140,7 @@
         <v>0</v>
       </c>
       <c r="BD363" s="36"/>
-      <c r="BE363" s="45"/>
+      <c r="BE363" s="44"/>
       <c r="BH363" s="37"/>
       <c r="BI363" s="37"/>
       <c r="BJ363" s="37"/>
@@ -69199,7 +68990,7 @@
         <v>0</v>
       </c>
       <c r="BD368" s="36"/>
-      <c r="BE368" s="45"/>
+      <c r="BE368" s="44"/>
       <c r="BH368" s="37"/>
       <c r="BI368" s="37"/>
       <c r="BJ368" s="37"/>
@@ -69539,7 +69330,7 @@
         <v>0</v>
       </c>
       <c r="BD370" s="36"/>
-      <c r="BE370" s="45"/>
+      <c r="BE370" s="44"/>
       <c r="BH370" s="37"/>
       <c r="BI370" s="37"/>
       <c r="BJ370" s="37"/>
@@ -70049,7 +69840,7 @@
         <v>0</v>
       </c>
       <c r="BD373" s="36"/>
-      <c r="BE373" s="45"/>
+      <c r="BE373" s="44"/>
       <c r="BH373" s="37"/>
       <c r="BI373" s="37"/>
       <c r="BJ373" s="37"/>
@@ -70219,7 +70010,7 @@
         <v>0</v>
       </c>
       <c r="BD374" s="36"/>
-      <c r="BE374" s="45"/>
+      <c r="BE374" s="44"/>
       <c r="BH374" s="37"/>
       <c r="BI374" s="37"/>
       <c r="BJ374" s="37"/>
@@ -70389,7 +70180,7 @@
         <v>0</v>
       </c>
       <c r="BD375" s="36"/>
-      <c r="BE375" s="45"/>
+      <c r="BE375" s="44"/>
       <c r="BH375" s="37"/>
       <c r="BI375" s="37"/>
       <c r="BJ375" s="37"/>
@@ -71239,7 +71030,7 @@
         <v>0</v>
       </c>
       <c r="BD380" s="36"/>
-      <c r="BE380" s="45"/>
+      <c r="BE380" s="44"/>
       <c r="BH380" s="37"/>
       <c r="BI380" s="37"/>
       <c r="BJ380" s="37"/>
@@ -71749,7 +71540,7 @@
         <v>0</v>
       </c>
       <c r="BD383" s="36"/>
-      <c r="BE383" s="45"/>
+      <c r="BE383" s="44"/>
       <c r="BH383" s="37"/>
       <c r="BI383" s="37"/>
       <c r="BJ383" s="37"/>
@@ -71919,7 +71710,7 @@
         <v>0</v>
       </c>
       <c r="BD384" s="36"/>
-      <c r="BE384" s="45"/>
+      <c r="BE384" s="44"/>
       <c r="BH384" s="37"/>
       <c r="BI384" s="37"/>
       <c r="BJ384" s="37"/>
@@ -72089,7 +71880,7 @@
         <v>0</v>
       </c>
       <c r="BD385" s="36"/>
-      <c r="BE385" s="45"/>
+      <c r="BE385" s="44"/>
       <c r="BH385" s="37"/>
       <c r="BI385" s="37"/>
       <c r="BJ385" s="37"/>
@@ -72429,7 +72220,7 @@
         <v>0</v>
       </c>
       <c r="BD387" s="36"/>
-      <c r="BE387" s="45"/>
+      <c r="BE387" s="44"/>
       <c r="BH387" s="37"/>
       <c r="BI387" s="37"/>
       <c r="BJ387" s="37"/>
@@ -72448,7 +72239,7 @@
       <c r="B388" s="27" t="s">
         <v>1210</v>
       </c>
-      <c r="C388" s="46" t="s">
+      <c r="C388" s="45" t="s">
         <v>1211</v>
       </c>
       <c r="D388" s="26" t="s">
@@ -72939,7 +72730,7 @@
         <v>0</v>
       </c>
       <c r="BD390" s="36"/>
-      <c r="BE390" s="45"/>
+      <c r="BE390" s="44"/>
       <c r="BH390" s="37"/>
       <c r="BI390" s="37"/>
       <c r="BJ390" s="37"/>
@@ -73619,7 +73410,7 @@
         <v>0</v>
       </c>
       <c r="BD394" s="36"/>
-      <c r="BE394" s="45"/>
+      <c r="BE394" s="44"/>
       <c r="BH394" s="37"/>
       <c r="BI394" s="37"/>
       <c r="BJ394" s="37"/>
@@ -73789,7 +73580,7 @@
         <v>0</v>
       </c>
       <c r="BD395" s="36"/>
-      <c r="BE395" s="45"/>
+      <c r="BE395" s="44"/>
       <c r="BH395" s="37"/>
       <c r="BI395" s="37"/>
       <c r="BJ395" s="37"/>
@@ -73959,7 +73750,7 @@
         <v>0</v>
       </c>
       <c r="BD396" s="36"/>
-      <c r="BE396" s="45"/>
+      <c r="BE396" s="44"/>
       <c r="BH396" s="37"/>
       <c r="BI396" s="37"/>
       <c r="BJ396" s="37"/>
@@ -74129,7 +73920,7 @@
         <v>0</v>
       </c>
       <c r="BD397" s="36"/>
-      <c r="BE397" s="45"/>
+      <c r="BE397" s="44"/>
       <c r="BH397" s="37"/>
       <c r="BI397" s="37"/>
       <c r="BJ397" s="37"/>
@@ -74299,7 +74090,7 @@
         <v>0</v>
       </c>
       <c r="BD398" s="36"/>
-      <c r="BE398" s="45"/>
+      <c r="BE398" s="44"/>
       <c r="BH398" s="37"/>
       <c r="BI398" s="37"/>
       <c r="BJ398" s="37"/>
@@ -75149,7 +74940,7 @@
         <v>0</v>
       </c>
       <c r="BD403" s="36"/>
-      <c r="BE403" s="45"/>
+      <c r="BE403" s="44"/>
       <c r="BH403" s="37"/>
       <c r="BI403" s="37"/>
       <c r="BJ403" s="37"/>
@@ -75319,7 +75110,7 @@
         <v>0</v>
       </c>
       <c r="BD404" s="36"/>
-      <c r="BE404" s="45"/>
+      <c r="BE404" s="44"/>
       <c r="BH404" s="37"/>
       <c r="BI404" s="37"/>
       <c r="BJ404" s="37"/>
@@ -75489,7 +75280,7 @@
         <v>0</v>
       </c>
       <c r="BD405" s="36"/>
-      <c r="BE405" s="45"/>
+      <c r="BE405" s="44"/>
       <c r="BH405" s="37"/>
       <c r="BI405" s="37"/>
       <c r="BJ405" s="37"/>
@@ -75659,7 +75450,7 @@
         <v>0</v>
       </c>
       <c r="BD406" s="36"/>
-      <c r="BE406" s="45"/>
+      <c r="BE406" s="44"/>
       <c r="BH406" s="37"/>
       <c r="BI406" s="37"/>
       <c r="BJ406" s="37"/>
@@ -76339,7 +76130,7 @@
         <v>0</v>
       </c>
       <c r="BD410" s="36"/>
-      <c r="BE410" s="45"/>
+      <c r="BE410" s="44"/>
       <c r="BH410" s="37"/>
       <c r="BI410" s="37"/>
       <c r="BJ410" s="37"/>
@@ -76679,7 +76470,7 @@
         <v>0</v>
       </c>
       <c r="BD412" s="36"/>
-      <c r="BE412" s="45"/>
+      <c r="BE412" s="44"/>
       <c r="BH412" s="37"/>
       <c r="BI412" s="37"/>
       <c r="BJ412" s="37"/>
@@ -77019,7 +76810,7 @@
         <v>0</v>
       </c>
       <c r="BD414" s="36"/>
-      <c r="BE414" s="45"/>
+      <c r="BE414" s="44"/>
       <c r="BH414" s="37"/>
       <c r="BI414" s="37"/>
       <c r="BJ414" s="37"/>
@@ -77359,7 +77150,7 @@
         <v>0</v>
       </c>
       <c r="BD416" s="36"/>
-      <c r="BE416" s="45"/>
+      <c r="BE416" s="44"/>
       <c r="BH416" s="37"/>
       <c r="BI416" s="37"/>
       <c r="BJ416" s="37"/>
@@ -77529,7 +77320,7 @@
         <v>0</v>
       </c>
       <c r="BD417" s="36"/>
-      <c r="BE417" s="45"/>
+      <c r="BE417" s="44"/>
       <c r="BH417" s="37"/>
       <c r="BI417" s="37"/>
       <c r="BJ417" s="37"/>
@@ -77869,7 +77660,7 @@
         <v>0</v>
       </c>
       <c r="BD419" s="36"/>
-      <c r="BE419" s="45"/>
+      <c r="BE419" s="44"/>
       <c r="BH419" s="37"/>
       <c r="BI419" s="37"/>
       <c r="BJ419" s="37"/>
@@ -78209,7 +78000,7 @@
         <v>0</v>
       </c>
       <c r="BD421" s="36"/>
-      <c r="BE421" s="45"/>
+      <c r="BE421" s="44"/>
       <c r="BH421" s="37"/>
       <c r="BI421" s="37"/>
       <c r="BJ421" s="37"/>
@@ -79059,7 +78850,7 @@
         <v>0</v>
       </c>
       <c r="BD426" s="36"/>
-      <c r="BE426" s="45"/>
+      <c r="BE426" s="44"/>
       <c r="BH426" s="37"/>
       <c r="BI426" s="37"/>
       <c r="BJ426" s="37"/>
@@ -79399,7 +79190,7 @@
         <v>0</v>
       </c>
       <c r="BD428" s="36"/>
-      <c r="BE428" s="45"/>
+      <c r="BE428" s="44"/>
       <c r="BH428" s="37"/>
       <c r="BI428" s="37"/>
       <c r="BJ428" s="37"/>
@@ -79569,7 +79360,7 @@
         <v>0</v>
       </c>
       <c r="BD429" s="36"/>
-      <c r="BE429" s="45"/>
+      <c r="BE429" s="44"/>
       <c r="BH429" s="37"/>
       <c r="BI429" s="37"/>
       <c r="BJ429" s="37"/>
@@ -79739,7 +79530,7 @@
         <v>0</v>
       </c>
       <c r="BD430" s="36"/>
-      <c r="BE430" s="45"/>
+      <c r="BE430" s="44"/>
       <c r="BH430" s="37"/>
       <c r="BI430" s="37"/>
       <c r="BJ430" s="37"/>
@@ -80079,7 +79870,7 @@
         <v>0</v>
       </c>
       <c r="BD432" s="36"/>
-      <c r="BE432" s="45"/>
+      <c r="BE432" s="44"/>
       <c r="BH432" s="37"/>
       <c r="BI432" s="37"/>
       <c r="BJ432" s="37"/>
@@ -80249,7 +80040,7 @@
         <v>0</v>
       </c>
       <c r="BD433" s="36"/>
-      <c r="BE433" s="45"/>
+      <c r="BE433" s="44"/>
       <c r="BH433" s="37"/>
       <c r="BI433" s="37"/>
       <c r="BJ433" s="37"/>
@@ -80271,7 +80062,7 @@
       <c r="C434" s="27" t="s">
         <v>1349</v>
       </c>
-      <c r="D434" s="47" t="s">
+      <c r="D434" s="46" t="s">
         <v>1350</v>
       </c>
       <c r="E434" s="28" t="s">
@@ -80415,7 +80206,7 @@
       <c r="C435" s="27" t="s">
         <v>1353</v>
       </c>
-      <c r="D435" s="47" t="s">
+      <c r="D435" s="46" t="s">
         <v>1354</v>
       </c>
       <c r="E435" s="28" t="s">
@@ -80559,7 +80350,7 @@
       <c r="C436" s="27" t="s">
         <v>1356</v>
       </c>
-      <c r="D436" s="47" t="s">
+      <c r="D436" s="46" t="s">
         <v>1357</v>
       </c>
       <c r="E436" s="28" t="s">
@@ -80703,7 +80494,7 @@
       <c r="C437" s="27" t="s">
         <v>1359</v>
       </c>
-      <c r="D437" s="47" t="s">
+      <c r="D437" s="46" t="s">
         <v>1360</v>
       </c>
       <c r="E437" s="28" t="s">
@@ -80847,7 +80638,7 @@
       <c r="C438" s="27" t="s">
         <v>1362</v>
       </c>
-      <c r="D438" s="47" t="s">
+      <c r="D438" s="46" t="s">
         <v>1363</v>
       </c>
       <c r="E438" s="28" t="s">
@@ -80991,7 +80782,7 @@
       <c r="C439" s="27" t="s">
         <v>1365</v>
       </c>
-      <c r="D439" s="47" t="s">
+      <c r="D439" s="46" t="s">
         <v>1366</v>
       </c>
       <c r="E439" s="28" t="s">
@@ -81135,7 +80926,7 @@
       <c r="C440" s="27" t="s">
         <v>1368</v>
       </c>
-      <c r="D440" s="47" t="s">
+      <c r="D440" s="46" t="s">
         <v>1369</v>
       </c>
       <c r="E440" s="28" t="s">
@@ -81279,7 +81070,7 @@
       <c r="C441" s="27" t="s">
         <v>1371</v>
       </c>
-      <c r="D441" s="47" t="s">
+      <c r="D441" s="46" t="s">
         <v>1372</v>
       </c>
       <c r="E441" s="28" t="s">
@@ -81423,7 +81214,7 @@
       <c r="C442" s="27" t="s">
         <v>1374</v>
       </c>
-      <c r="D442" s="47" t="s">
+      <c r="D442" s="46" t="s">
         <v>1375</v>
       </c>
       <c r="E442" s="28" t="s">
@@ -81567,7 +81358,7 @@
       <c r="C443" s="27" t="s">
         <v>1377</v>
       </c>
-      <c r="D443" s="47" t="s">
+      <c r="D443" s="46" t="s">
         <v>1378</v>
       </c>
       <c r="E443" s="28" t="s">
@@ -88805,7 +88596,7 @@
         <v>2.7057973010190031</v>
       </c>
       <c r="BB484" s="35"/>
-      <c r="BC484" s="48">
+      <c r="BC484" s="47">
         <v>37800</v>
       </c>
       <c r="BD484" s="36"/>
@@ -88821,7 +88612,7 @@
       <c r="C485" s="27" t="s">
         <v>1503</v>
       </c>
-      <c r="D485" s="47" t="s">
+      <c r="D485" s="46" t="s">
         <v>1504</v>
       </c>
       <c r="E485" s="28">
@@ -88919,7 +88710,7 @@
         <v>3.2691608419861824</v>
       </c>
       <c r="BB485" s="35"/>
-      <c r="BC485" s="48">
+      <c r="BC485" s="47">
         <v>12000</v>
       </c>
       <c r="BD485" s="36"/>
@@ -91356,158 +91147,78 @@
   <mergeCells count="1">
     <mergeCell ref="AT1:BB1"/>
   </mergeCells>
+  <conditionalFormatting sqref="C1:C499">
+    <cfRule type="duplicateValues" dxfId="22" priority="319"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C335:C387 C168:C333 C389:C499 C1:C164">
+    <cfRule type="duplicateValues" dxfId="21" priority="314"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C335:C387 C168:C333 C389:C499 C3:C164">
+    <cfRule type="duplicateValues" dxfId="20" priority="309"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C490:C499">
+    <cfRule type="duplicateValues" dxfId="19" priority="130"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D10">
+    <cfRule type="duplicateValues" dxfId="18" priority="320"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17">
+    <cfRule type="duplicateValues" dxfId="17" priority="321"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D36">
+    <cfRule type="duplicateValues" dxfId="16" priority="322"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D49">
+    <cfRule type="duplicateValues" dxfId="15" priority="323"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D51">
+    <cfRule type="duplicateValues" dxfId="14" priority="324"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D61">
+    <cfRule type="duplicateValues" dxfId="13" priority="325"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D75">
+    <cfRule type="duplicateValues" dxfId="12" priority="326"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D92">
+    <cfRule type="duplicateValues" dxfId="11" priority="327"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D103">
+    <cfRule type="duplicateValues" dxfId="10" priority="328"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D115">
+    <cfRule type="duplicateValues" dxfId="9" priority="329"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D122">
+    <cfRule type="duplicateValues" dxfId="8" priority="330"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D141">
+    <cfRule type="duplicateValues" dxfId="7" priority="331"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D145">
+    <cfRule type="duplicateValues" dxfId="6" priority="332"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D152">
+    <cfRule type="duplicateValues" dxfId="5" priority="333"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D165:D167">
+    <cfRule type="duplicateValues" dxfId="4" priority="76"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AR3:AS499">
-    <cfRule type="cellIs" dxfId="42" priority="58" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="38" operator="lessThan">
       <formula>-0.3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="59" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="39" operator="greaterThan">
       <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA3:BA499">
-    <cfRule type="cellIs" dxfId="40" priority="56" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="36" operator="greaterThan">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="57" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="37" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AR262:AS433">
-    <cfRule type="cellIs" dxfId="38" priority="54" operator="lessThan">
-      <formula>-0.3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="55" operator="greaterThan">
-      <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BA262:BA433">
-    <cfRule type="cellIs" dxfId="36" priority="52" operator="greaterThan">
-      <formula>4</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="53" operator="lessThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AR59:AS59">
-    <cfRule type="cellIs" dxfId="34" priority="50" operator="lessThan">
-      <formula>-0.3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="51" operator="greaterThan">
-      <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BA59">
-    <cfRule type="cellIs" dxfId="32" priority="48" operator="greaterThan">
-      <formula>4</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="49" operator="lessThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AR245:AS254">
-    <cfRule type="cellIs" dxfId="30" priority="46" operator="lessThan">
-      <formula>-0.3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="47" operator="greaterThan">
-      <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BA245:BA254">
-    <cfRule type="cellIs" dxfId="28" priority="44" operator="greaterThan">
-      <formula>4</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="45" operator="lessThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AR209:AS211">
-    <cfRule type="cellIs" dxfId="26" priority="42" operator="lessThan">
-      <formula>-0.3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="43" operator="greaterThan">
-      <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BA209:BA211">
-    <cfRule type="cellIs" dxfId="24" priority="40" operator="greaterThan">
-      <formula>4</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="41" operator="lessThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AR165:AS167">
-    <cfRule type="cellIs" dxfId="22" priority="38" operator="lessThan">
-      <formula>-0.3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="39" operator="greaterThan">
-      <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BA165:BA167">
-    <cfRule type="cellIs" dxfId="20" priority="36" operator="greaterThan">
-      <formula>4</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="37" operator="lessThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D165:D167">
-    <cfRule type="duplicateValues" dxfId="18" priority="76"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C490:C499">
-    <cfRule type="duplicateValues" dxfId="17" priority="130"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C335:C387 C168:C333 C389:C499 C3:C164">
-    <cfRule type="duplicateValues" dxfId="16" priority="309"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C335:C387 C168:C333 C389:C499 C1:C164">
-    <cfRule type="duplicateValues" dxfId="15" priority="314"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C499">
-    <cfRule type="duplicateValues" dxfId="14" priority="319"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D10">
-    <cfRule type="duplicateValues" dxfId="13" priority="320"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D17">
-    <cfRule type="duplicateValues" dxfId="12" priority="321"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D36">
-    <cfRule type="duplicateValues" dxfId="11" priority="322"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D49">
-    <cfRule type="duplicateValues" dxfId="10" priority="323"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D51">
-    <cfRule type="duplicateValues" dxfId="9" priority="324"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D61">
-    <cfRule type="duplicateValues" dxfId="8" priority="325"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D75">
-    <cfRule type="duplicateValues" dxfId="7" priority="326"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D92">
-    <cfRule type="duplicateValues" dxfId="6" priority="327"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D103">
-    <cfRule type="duplicateValues" dxfId="5" priority="328"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D115">
-    <cfRule type="duplicateValues" dxfId="4" priority="329"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D122">
-    <cfRule type="duplicateValues" dxfId="3" priority="330"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D141">
-    <cfRule type="duplicateValues" dxfId="2" priority="331"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D145">
-    <cfRule type="duplicateValues" dxfId="1" priority="332"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D152">
-    <cfRule type="duplicateValues" dxfId="0" priority="333"/>
   </conditionalFormatting>
   <pageMargins left="0.74803149606299213" right="0.98425196850393704" top="0.74803149606299213" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="140" orientation="landscape" verticalDpi="0" r:id="rId1"/>
@@ -91518,809 +91229,809 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{018FFF47-CABB-423E-BC52-71DB5175FF16}">
   <dimension ref="A3:O23"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" style="51"/>
-    <col min="2" max="9" width="21" style="51" customWidth="1"/>
-    <col min="10" max="10" width="24.33203125" style="51" customWidth="1"/>
-    <col min="11" max="14" width="21" style="51" customWidth="1"/>
-    <col min="15" max="15" width="17.1640625" style="51" customWidth="1"/>
-    <col min="16" max="16384" width="9.33203125" style="51"/>
+    <col min="1" max="1" width="9.28515625" style="50"/>
+    <col min="2" max="9" width="21" style="50" customWidth="1"/>
+    <col min="10" max="10" width="24.28515625" style="50" customWidth="1"/>
+    <col min="11" max="14" width="21" style="50" customWidth="1"/>
+    <col min="15" max="15" width="17.140625" style="50" customWidth="1"/>
+    <col min="16" max="16384" width="9.28515625" style="50"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="51" t="s">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="50" t="s">
         <v>1565</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="49" t="s">
         <v>1548</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="49" t="s">
         <v>1549</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="49" t="s">
         <v>1550</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="E3" s="49" t="s">
         <v>1551</v>
       </c>
-      <c r="F3" s="50" t="s">
+      <c r="F3" s="49" t="s">
         <v>1552</v>
       </c>
-      <c r="G3" s="50" t="s">
+      <c r="G3" s="49" t="s">
         <v>1553</v>
       </c>
-      <c r="H3" s="50" t="s">
+      <c r="H3" s="49" t="s">
         <v>1554</v>
       </c>
-      <c r="I3" s="50" t="s">
+      <c r="I3" s="49" t="s">
         <v>1555</v>
       </c>
-      <c r="J3" s="50" t="s">
+      <c r="J3" s="49" t="s">
         <v>1556</v>
       </c>
-      <c r="K3" s="50" t="s">
+      <c r="K3" s="49" t="s">
         <v>1557</v>
       </c>
-      <c r="L3" s="50" t="s">
+      <c r="L3" s="49" t="s">
         <v>1558</v>
       </c>
-      <c r="M3" s="50" t="s">
+      <c r="M3" s="49" t="s">
         <v>1559</v>
       </c>
-      <c r="N3" s="50" t="s">
+      <c r="N3" s="49" t="s">
         <v>1566</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A4" s="51">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="50">
         <v>2024</v>
       </c>
-      <c r="B4" s="61">
+      <c r="B4" s="60">
         <v>24596427</v>
       </c>
-      <c r="C4" s="61">
+      <c r="C4" s="60">
         <v>22395512</v>
       </c>
-      <c r="D4" s="61">
+      <c r="D4" s="60">
         <v>44147660</v>
       </c>
-      <c r="E4" s="61">
+      <c r="E4" s="60">
         <v>62276496.32</v>
       </c>
-      <c r="F4" s="61">
+      <c r="F4" s="60">
         <v>73462110</v>
       </c>
-      <c r="G4" s="61">
+      <c r="G4" s="60">
         <v>68345412</v>
       </c>
-      <c r="H4" s="61">
+      <c r="H4" s="60">
         <v>71289315.980000004</v>
       </c>
-      <c r="I4" s="61">
+      <c r="I4" s="60">
         <v>91399515.640000001</v>
       </c>
-      <c r="J4" s="61">
+      <c r="J4" s="60">
         <v>99082123</v>
       </c>
-      <c r="K4" s="61">
+      <c r="K4" s="60">
         <v>88432469</v>
       </c>
-      <c r="L4" s="61">
+      <c r="L4" s="60">
         <v>82883679</v>
       </c>
-      <c r="M4" s="61">
+      <c r="M4" s="60">
         <v>65881945</v>
       </c>
-      <c r="N4" s="51">
+      <c r="N4" s="50">
         <f>SUM(B4:M4)</f>
         <v>794192664.94000006</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="51">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="50">
         <v>2025</v>
       </c>
-      <c r="B5" s="61">
+      <c r="B5" s="60">
         <v>60612221</v>
       </c>
-      <c r="C5" s="61">
+      <c r="C5" s="60">
         <v>70526214</v>
       </c>
-      <c r="D5" s="61">
+      <c r="D5" s="60">
         <v>62394638.899999999</v>
       </c>
-      <c r="E5" s="61">
+      <c r="E5" s="60">
         <v>80289436.030000001</v>
       </c>
-      <c r="F5" s="61">
+      <c r="F5" s="60">
         <v>77227054</v>
       </c>
-      <c r="G5" s="61">
+      <c r="G5" s="60">
         <v>80386586</v>
       </c>
-      <c r="H5" s="61">
+      <c r="H5" s="60">
         <v>79580845.349999994</v>
       </c>
-      <c r="I5" s="61">
+      <c r="I5" s="60">
         <v>85147826.950000003</v>
       </c>
-      <c r="J5" s="61">
+      <c r="J5" s="60">
         <v>75393744</v>
       </c>
-      <c r="K5" s="61">
+      <c r="K5" s="60">
         <v>70827551</v>
       </c>
-      <c r="L5" s="61">
+      <c r="L5" s="60">
         <v>72949510</v>
       </c>
-      <c r="M5" s="61">
+      <c r="M5" s="60">
         <v>71608529.439999998</v>
       </c>
-      <c r="N5" s="51">
+      <c r="N5" s="50">
         <f>SUM(B5:M5)</f>
         <v>886944156.67000008</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A6" s="51">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="50">
         <v>2026</v>
       </c>
-      <c r="B6" s="61">
+      <c r="B6" s="60">
         <v>51463402</v>
       </c>
-      <c r="C6" s="61">
+      <c r="C6" s="60">
         <v>57127585</v>
       </c>
-      <c r="D6" s="61">
+      <c r="D6" s="60">
         <v>49906664.43</v>
       </c>
-      <c r="E6" s="61">
+      <c r="E6" s="60">
         <v>61255146</v>
       </c>
-      <c r="F6" s="61">
+      <c r="F6" s="60">
         <v>59215517</v>
       </c>
-      <c r="G6" s="61">
+      <c r="G6" s="60">
         <v>68110627</v>
       </c>
-      <c r="H6" s="61">
+      <c r="H6" s="60">
         <v>72110849.170000002</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="60">
         <v>70105174.180000007</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="60">
         <v>45371784.460000001</v>
       </c>
-      <c r="N6" s="51">
+      <c r="N6" s="50">
         <f>SUM(B6:M6)</f>
         <v>534666749.24000001</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B8" s="50" t="s">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B8" s="49" t="s">
         <v>1567</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B10" s="52" t="s">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B10" s="51" t="s">
         <v>1561</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="52" t="s">
+      <c r="D10" s="51" t="s">
         <v>1562</v>
       </c>
-      <c r="E10" s="52" t="s">
+      <c r="E10" s="51" t="s">
         <v>1563</v>
       </c>
-      <c r="F10" s="52" t="s">
+      <c r="F10" s="51" t="s">
         <v>1570</v>
       </c>
-      <c r="G10" s="52" t="s">
+      <c r="G10" s="51" t="s">
         <v>1571</v>
       </c>
-      <c r="H10" s="52" t="s">
+      <c r="H10" s="51" t="s">
         <v>1572</v>
       </c>
-      <c r="I10" s="52" t="s">
+      <c r="I10" s="51" t="s">
         <v>1573</v>
       </c>
-      <c r="J10" s="52" t="s">
+      <c r="J10" s="51" t="s">
         <v>1574</v>
       </c>
-      <c r="K10" s="52" t="s">
+      <c r="K10" s="51" t="s">
         <v>1575</v>
       </c>
-      <c r="M10" s="52" t="s">
+      <c r="M10" s="51" t="s">
         <v>1568</v>
       </c>
-      <c r="N10" s="52" t="s">
+      <c r="N10" s="51" t="s">
         <v>1569</v>
       </c>
-      <c r="O10" s="52" t="s">
+      <c r="O10" s="51" t="s">
         <v>1560</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B11" s="51" t="str" cm="1">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B11" s="50" t="str" cm="1">
         <f t="array" ref="B11">INDEX($B$3:$M$3,ROW()-10)</f>
         <v>янв</v>
       </c>
-      <c r="C11" s="53" cm="1">
+      <c r="C11" s="52" cm="1">
         <f t="array" ref="C11">INDEX($B$4:$M$4,ROW()-10)</f>
         <v>24596427</v>
       </c>
-      <c r="D11" s="54">
+      <c r="D11" s="53">
         <f>IFERROR(C11/$N$11,"")</f>
         <v>0.37164423323186774</v>
       </c>
-      <c r="E11" s="55">
+      <c r="E11" s="54">
         <f>IFERROR(C11/$O$11,"")</f>
         <v>3.0970352769322314E-2</v>
       </c>
-      <c r="F11" s="53" cm="1">
+      <c r="F11" s="52" cm="1">
         <f t="array" ref="F11">INDEX($B$5:$M$5,ROW()-10)</f>
         <v>60612221</v>
       </c>
-      <c r="G11" s="54">
+      <c r="G11" s="53">
         <f>IFERROR(F11/$N$12,"")</f>
         <v>0.82005912833429884</v>
       </c>
-      <c r="H11" s="55">
+      <c r="H11" s="54">
         <f>IFERROR(F11/$O$12,"")</f>
         <v>6.8338260694524894E-2</v>
       </c>
-      <c r="I11" s="53" cm="1">
+      <c r="I11" s="52" cm="1">
         <f t="array" ref="I11">INDEX($B$6:$M$6,ROW()-10)</f>
         <v>51463402</v>
       </c>
-      <c r="J11" s="54">
+      <c r="J11" s="53">
         <f>IFERROR(I11/$N$13,"")</f>
         <v>0.86627907693600192</v>
       </c>
-      <c r="K11" s="55">
+      <c r="K11" s="54">
         <f>IFERROR(I11/$O$13,"")</f>
         <v>9.6253230770666873E-2</v>
       </c>
-      <c r="M11" s="56">
+      <c r="M11" s="55">
         <f>$A$4</f>
         <v>2024</v>
       </c>
-      <c r="N11" s="57">
+      <c r="N11" s="56">
         <f>IFERROR(AVERAGE($B$4:$M$4),"")</f>
         <v>66182722.078333341</v>
       </c>
-      <c r="O11" s="53">
+      <c r="O11" s="52">
         <f>$N$4</f>
         <v>794192664.94000006</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B12" s="51" t="str" cm="1">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B12" s="50" t="str" cm="1">
         <f t="array" ref="B12">INDEX($B$3:$M$3,ROW()-10)</f>
         <v>фев</v>
       </c>
-      <c r="C12" s="53" cm="1">
+      <c r="C12" s="52" cm="1">
         <f t="array" ref="C12">INDEX($B$4:$M$4,ROW()-10)</f>
         <v>22395512</v>
       </c>
-      <c r="D12" s="54">
+      <c r="D12" s="53">
         <f t="shared" ref="D12:D22" si="0">IFERROR(C12/$N$11,"")</f>
         <v>0.33838910363180363</v>
       </c>
-      <c r="E12" s="55">
+      <c r="E12" s="54">
         <f t="shared" ref="E12:E22" si="1">IFERROR(C12/$O$11,"")</f>
         <v>2.8199091969316973E-2</v>
       </c>
-      <c r="F12" s="53" cm="1">
+      <c r="F12" s="52" cm="1">
         <f t="array" ref="F12">INDEX($B$5:$M$5,ROW()-10)</f>
         <v>70526214</v>
       </c>
-      <c r="G12" s="54">
+      <c r="G12" s="53">
         <f t="shared" ref="G12:G22" si="2">IFERROR(F12/$N$12,"")</f>
         <v>0.9541914918042389</v>
       </c>
-      <c r="H12" s="55">
+      <c r="H12" s="54">
         <f t="shared" ref="H12:H22" si="3">IFERROR(F12/$O$12,"")</f>
         <v>7.9515957650353242E-2</v>
       </c>
-      <c r="I12" s="53" cm="1">
+      <c r="I12" s="52" cm="1">
         <f t="array" ref="I12">INDEX($B$6:$M$6,ROW()-10)</f>
         <v>57127585</v>
       </c>
-      <c r="J12" s="54">
+      <c r="J12" s="53">
         <f t="shared" ref="J12:J22" si="4">IFERROR(I12/$N$13,"")</f>
         <v>0.96162378852029617</v>
       </c>
-      <c r="K12" s="55">
+      <c r="K12" s="54">
         <f t="shared" ref="K12:K22" si="5">IFERROR(I12/$O$13,"")</f>
         <v>0.10684708761336624</v>
       </c>
-      <c r="M12" s="56">
+      <c r="M12" s="55">
         <f>$A$5</f>
         <v>2025</v>
       </c>
-      <c r="N12" s="57">
+      <c r="N12" s="56">
         <f>IFERROR(AVERAGE($B$5:$M$5),"")</f>
         <v>73912013.05583334</v>
       </c>
-      <c r="O12" s="53">
+      <c r="O12" s="52">
         <f>$N$5</f>
         <v>886944156.67000008</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B13" s="51" t="str" cm="1">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B13" s="50" t="str" cm="1">
         <f t="array" ref="B13">INDEX($B$3:$M$3,ROW()-10)</f>
         <v>мар</v>
       </c>
-      <c r="C13" s="53" cm="1">
+      <c r="C13" s="52" cm="1">
         <f t="array" ref="C13">INDEX($B$4:$M$4,ROW()-10)</f>
         <v>44147660</v>
       </c>
-      <c r="D13" s="54">
+      <c r="D13" s="53">
         <f t="shared" si="0"/>
         <v>0.66705718069056119</v>
       </c>
-      <c r="E13" s="55">
+      <c r="E13" s="54">
         <f t="shared" si="1"/>
         <v>5.5588098390880109E-2</v>
       </c>
-      <c r="F13" s="53" cm="1">
+      <c r="F13" s="52" cm="1">
         <f t="array" ref="F13">INDEX($B$5:$M$5,ROW()-10)</f>
         <v>62394638.899999999</v>
       </c>
-      <c r="G13" s="54">
+      <c r="G13" s="53">
         <f t="shared" si="2"/>
         <v>0.84417453023322364</v>
       </c>
-      <c r="H13" s="55">
+      <c r="H13" s="54">
         <f t="shared" si="3"/>
         <v>7.0347877519435303E-2</v>
       </c>
-      <c r="I13" s="53" cm="1">
+      <c r="I13" s="52" cm="1">
         <f t="array" ref="I13">INDEX($B$6:$M$6,ROW()-10)</f>
         <v>49906664.43</v>
       </c>
-      <c r="J13" s="54">
+      <c r="J13" s="53">
         <f t="shared" si="4"/>
         <v>0.84007464557774858</v>
       </c>
-      <c r="K13" s="55">
+      <c r="K13" s="54">
         <f t="shared" si="5"/>
         <v>9.3341627286416512E-2</v>
       </c>
-      <c r="M13" s="56">
+      <c r="M13" s="55">
         <f>$A$6</f>
         <v>2026</v>
       </c>
-      <c r="N13" s="57">
+      <c r="N13" s="56">
         <f>IFERROR(AVERAGE($B$6:$M$6),"")</f>
         <v>59407416.582222223</v>
       </c>
-      <c r="O13" s="53">
+      <c r="O13" s="52">
         <f>$N$6</f>
         <v>534666749.24000001</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B14" s="51" t="str" cm="1">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B14" s="50" t="str" cm="1">
         <f t="array" ref="B14">INDEX($B$3:$M$3,ROW()-10)</f>
         <v>апр</v>
       </c>
-      <c r="C14" s="53" cm="1">
+      <c r="C14" s="52" cm="1">
         <f t="array" ref="C14">INDEX($B$4:$M$4,ROW()-10)</f>
         <v>62276496.32</v>
       </c>
-      <c r="D14" s="54">
+      <c r="D14" s="53">
         <f t="shared" si="0"/>
         <v>0.94097816415423408</v>
       </c>
-      <c r="E14" s="55">
+      <c r="E14" s="54">
         <f t="shared" si="1"/>
         <v>7.841484701285284E-2</v>
       </c>
-      <c r="F14" s="53" cm="1">
+      <c r="F14" s="52" cm="1">
         <f t="array" ref="F14">INDEX($B$5:$M$5,ROW()-10)</f>
         <v>80289436.030000001</v>
       </c>
-      <c r="G14" s="54">
+      <c r="G14" s="53">
         <f t="shared" si="2"/>
         <v>1.0862839843010248</v>
       </c>
-      <c r="H14" s="55">
+      <c r="H14" s="54">
         <f t="shared" si="3"/>
         <v>9.0523665358418728E-2</v>
       </c>
-      <c r="I14" s="53" cm="1">
+      <c r="I14" s="52" cm="1">
         <f t="array" ref="I14">INDEX($B$6:$M$6,ROW()-10)</f>
         <v>61255146</v>
       </c>
-      <c r="J14" s="54">
+      <c r="J14" s="53">
         <f t="shared" si="4"/>
         <v>1.0311026724284575</v>
       </c>
-      <c r="K14" s="55">
+      <c r="K14" s="54">
         <f t="shared" si="5"/>
         <v>0.11456696360316196</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B15" s="51" t="str" cm="1">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B15" s="50" t="str" cm="1">
         <f t="array" ref="B15">INDEX($B$3:$M$3,ROW()-10)</f>
         <v>май</v>
       </c>
-      <c r="C15" s="53" cm="1">
+      <c r="C15" s="52" cm="1">
         <f t="array" ref="C15">INDEX($B$4:$M$4,ROW()-10)</f>
         <v>73462110</v>
       </c>
-      <c r="D15" s="54">
+      <c r="D15" s="53">
         <f t="shared" si="0"/>
         <v>1.1099892493550028</v>
       </c>
-      <c r="E15" s="55">
+      <c r="E15" s="54">
         <f t="shared" si="1"/>
         <v>9.2499104112916911E-2</v>
       </c>
-      <c r="F15" s="53" cm="1">
+      <c r="F15" s="52" cm="1">
         <f t="array" ref="F15">INDEX($B$5:$M$5,ROW()-10)</f>
         <v>77227054</v>
       </c>
-      <c r="G15" s="54">
+      <c r="G15" s="53">
         <f t="shared" si="2"/>
         <v>1.0448511792211974</v>
       </c>
-      <c r="H15" s="55">
+      <c r="H15" s="54">
         <f t="shared" si="3"/>
         <v>8.7070931601766446E-2</v>
       </c>
-      <c r="I15" s="53" cm="1">
+      <c r="I15" s="52" cm="1">
         <f t="array" ref="I15">INDEX($B$6:$M$6,ROW()-10)</f>
         <v>59215517</v>
       </c>
-      <c r="J15" s="54">
+      <c r="J15" s="53">
         <f t="shared" si="4"/>
         <v>0.99676977062356131</v>
       </c>
-      <c r="K15" s="55">
+      <c r="K15" s="54">
         <f t="shared" si="5"/>
         <v>0.11075219673595126</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B16" s="51" t="str" cm="1">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B16" s="50" t="str" cm="1">
         <f t="array" ref="B16">INDEX($B$3:$M$3,ROW()-10)</f>
         <v>июн</v>
       </c>
-      <c r="C16" s="53" cm="1">
+      <c r="C16" s="52" cm="1">
         <f t="array" ref="C16">INDEX($B$4:$M$4,ROW()-10)</f>
         <v>68345412</v>
       </c>
-      <c r="D16" s="54">
+      <c r="D16" s="53">
         <f t="shared" si="0"/>
         <v>1.0326775607553118</v>
       </c>
-      <c r="E16" s="55">
+      <c r="E16" s="54">
         <f t="shared" si="1"/>
         <v>8.6056463396275998E-2</v>
       </c>
-      <c r="F16" s="53" cm="1">
+      <c r="F16" s="52" cm="1">
         <f t="array" ref="F16">INDEX($B$5:$M$5,ROW()-10)</f>
         <v>80386586</v>
       </c>
-      <c r="G16" s="54">
+      <c r="G16" s="53">
         <f t="shared" si="2"/>
         <v>1.08759838457215</v>
       </c>
-      <c r="H16" s="55">
+      <c r="H16" s="54">
         <f t="shared" si="3"/>
         <v>9.0633198714345831E-2</v>
       </c>
-      <c r="I16" s="53" cm="1">
+      <c r="I16" s="52" cm="1">
         <f t="array" ref="I16">INDEX($B$6:$M$6,ROW()-10)</f>
         <v>68110627</v>
       </c>
-      <c r="J16" s="54">
+      <c r="J16" s="53">
         <f t="shared" si="4"/>
         <v>1.1465004021127931</v>
       </c>
-      <c r="K16" s="55">
+      <c r="K16" s="54">
         <f t="shared" si="5"/>
         <v>0.12738893356808814</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B17" s="51" t="str" cm="1">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B17" s="50" t="str" cm="1">
         <f t="array" ref="B17">INDEX($B$3:$M$3,ROW()-10)</f>
         <v>июл</v>
       </c>
-      <c r="C17" s="53" cm="1">
+      <c r="C17" s="52" cm="1">
         <f t="array" ref="C17">INDEX($B$4:$M$4,ROW()-10)</f>
         <v>71289315.980000004</v>
       </c>
-      <c r="D17" s="54">
+      <c r="D17" s="53">
         <f t="shared" si="0"/>
         <v>1.0771590188693438</v>
       </c>
-      <c r="E17" s="55">
+      <c r="E17" s="54">
         <f t="shared" si="1"/>
         <v>8.9763251572445329E-2</v>
       </c>
-      <c r="F17" s="53" cm="1">
+      <c r="F17" s="52" cm="1">
         <f t="array" ref="F17">INDEX($B$5:$M$5,ROW()-10)</f>
         <v>79580845.349999994</v>
       </c>
-      <c r="G17" s="54">
+      <c r="G17" s="53">
         <f t="shared" si="2"/>
         <v>1.0766970355669301</v>
       </c>
-      <c r="H17" s="55">
+      <c r="H17" s="54">
         <f t="shared" si="3"/>
         <v>8.9724752963910845E-2</v>
       </c>
-      <c r="I17" s="53" cm="1">
+      <c r="I17" s="52" cm="1">
         <f t="array" ref="I17">INDEX($B$6:$M$6,ROW()-10)</f>
         <v>72110849.170000002</v>
       </c>
-      <c r="J17" s="54">
+      <c r="J17" s="53">
         <f t="shared" si="4"/>
         <v>1.2138358023058573</v>
       </c>
-      <c r="K17" s="55">
+      <c r="K17" s="54">
         <f t="shared" si="5"/>
         <v>0.1348706447006508</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B18" s="51" t="str" cm="1">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B18" s="50" t="str" cm="1">
         <f t="array" ref="B18">INDEX($B$3:$M$3,ROW()-10)</f>
         <v>авг</v>
       </c>
-      <c r="C18" s="53" cm="1">
+      <c r="C18" s="52" cm="1">
         <f t="array" ref="C18">INDEX($B$4:$M$4,ROW()-10)</f>
         <v>91399515.640000001</v>
       </c>
-      <c r="D18" s="54">
+      <c r="D18" s="53">
         <f t="shared" si="0"/>
         <v>1.3810177757847473</v>
       </c>
-      <c r="E18" s="55">
+      <c r="E18" s="54">
         <f t="shared" si="1"/>
         <v>0.11508481464872895</v>
       </c>
-      <c r="F18" s="53" cm="1">
+      <c r="F18" s="52" cm="1">
         <f t="array" ref="F18">INDEX($B$5:$M$5,ROW()-10)</f>
         <v>85147826.950000003</v>
       </c>
-      <c r="G18" s="54">
+      <c r="G18" s="53">
         <f t="shared" si="2"/>
         <v>1.1520160719432591</v>
       </c>
-      <c r="H18" s="55">
+      <c r="H18" s="54">
         <f t="shared" si="3"/>
         <v>9.6001339328604926E-2</v>
       </c>
-      <c r="I18" s="53" cm="1">
+      <c r="I18" s="52" cm="1">
         <f t="array" ref="I18">INDEX($B$6:$M$6,ROW()-10)</f>
         <v>70105174.180000007</v>
       </c>
-      <c r="J18" s="54">
+      <c r="J18" s="53">
         <f t="shared" si="4"/>
         <v>1.1800744454688021</v>
       </c>
-      <c r="K18" s="55">
+      <c r="K18" s="54">
         <f t="shared" si="5"/>
         <v>0.1311193828298669</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B19" s="51" t="str" cm="1">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="50" t="str" cm="1">
         <f t="array" ref="B19">INDEX($B$3:$M$3,ROW()-10)</f>
         <v>сен</v>
       </c>
-      <c r="C19" s="53" cm="1">
+      <c r="C19" s="52" cm="1">
         <f t="array" ref="C19">INDEX($B$4:$M$4,ROW()-10)</f>
         <v>99082123</v>
       </c>
-      <c r="D19" s="54">
+      <c r="D19" s="53">
         <f t="shared" si="0"/>
         <v>1.4970995433328838</v>
       </c>
-      <c r="E19" s="55">
+      <c r="E19" s="54">
         <f t="shared" si="1"/>
         <v>0.12475829527774031</v>
       </c>
-      <c r="F19" s="53" cm="1">
+      <c r="F19" s="52" cm="1">
         <f t="array" ref="F19">INDEX($B$5:$M$5,ROW()-10)</f>
         <v>75393744</v>
       </c>
-      <c r="G19" s="54">
+      <c r="G19" s="53">
         <f t="shared" si="2"/>
         <v>1.0200472275467232</v>
       </c>
-      <c r="H19" s="55">
+      <c r="H19" s="54">
         <f t="shared" si="3"/>
         <v>8.5003935628893593E-2</v>
       </c>
-      <c r="I19" s="53" cm="1">
+      <c r="I19" s="52" cm="1">
         <f t="array" ref="I19">INDEX($B$6:$M$6,ROW()-10)</f>
         <v>45371784.460000001</v>
       </c>
-      <c r="J19" s="54">
+      <c r="J19" s="53">
         <f t="shared" si="4"/>
         <v>0.76373939602648178</v>
       </c>
-      <c r="K19" s="55">
+      <c r="K19" s="54">
         <f t="shared" si="5"/>
         <v>8.4859932891831316E-2</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B20" s="51" t="str" cm="1">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B20" s="50" t="str" cm="1">
         <f t="array" ref="B20">INDEX($B$3:$M$3,ROW()-10)</f>
         <v>окт</v>
       </c>
-      <c r="C20" s="53" cm="1">
+      <c r="C20" s="52" cm="1">
         <f t="array" ref="C20">INDEX($B$4:$M$4,ROW()-10)</f>
         <v>88432469</v>
       </c>
-      <c r="D20" s="54">
+      <c r="D20" s="53">
         <f t="shared" si="0"/>
         <v>1.3361866393970927</v>
       </c>
-      <c r="E20" s="55">
+      <c r="E20" s="54">
         <f t="shared" si="1"/>
         <v>0.11134888661642441</v>
       </c>
-      <c r="F20" s="53" cm="1">
+      <c r="F20" s="52" cm="1">
         <f t="array" ref="F20">INDEX($B$5:$M$5,ROW()-10)</f>
         <v>70827551</v>
       </c>
-      <c r="G20" s="54">
+      <c r="G20" s="53">
         <f t="shared" si="2"/>
         <v>0.95826846099424556</v>
       </c>
-      <c r="H20" s="55">
+      <c r="H20" s="54">
         <f t="shared" si="3"/>
         <v>7.9855705082853792E-2</v>
       </c>
-      <c r="I20" s="53" cm="1">
+      <c r="I20" s="52" cm="1">
         <f t="array" ref="I20">INDEX($B$6:$M$6,ROW()-10)</f>
         <v>0</v>
       </c>
-      <c r="J20" s="54">
+      <c r="J20" s="53">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K20" s="55">
+      <c r="K20" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B21" s="51" t="str" cm="1">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B21" s="50" t="str" cm="1">
         <f t="array" ref="B21">INDEX($B$3:$M$3,ROW()-10)</f>
         <v>ноя</v>
       </c>
-      <c r="C21" s="53" cm="1">
+      <c r="C21" s="52" cm="1">
         <f t="array" ref="C21">INDEX($B$4:$M$4,ROW()-10)</f>
         <v>82883679</v>
       </c>
-      <c r="D21" s="54">
+      <c r="D21" s="53">
         <f t="shared" si="0"/>
         <v>1.2523461773285713</v>
       </c>
-      <c r="E21" s="55">
+      <c r="E21" s="54">
         <f t="shared" si="1"/>
         <v>0.10436218144404762</v>
       </c>
-      <c r="F21" s="53" cm="1">
+      <c r="F21" s="52" cm="1">
         <f t="array" ref="F21">INDEX($B$5:$M$5,ROW()-10)</f>
         <v>72949510</v>
       </c>
-      <c r="G21" s="54">
+      <c r="G21" s="53">
         <f t="shared" si="2"/>
         <v>0.98697771828909242</v>
       </c>
-      <c r="H21" s="55">
+      <c r="H21" s="54">
         <f t="shared" si="3"/>
         <v>8.2248143190757697E-2</v>
       </c>
-      <c r="I21" s="53" cm="1">
+      <c r="I21" s="52" cm="1">
         <f t="array" ref="I21">INDEX($B$6:$M$6,ROW()-10)</f>
         <v>0</v>
       </c>
-      <c r="J21" s="54">
+      <c r="J21" s="53">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K21" s="55">
+      <c r="K21" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B22" s="51" t="str" cm="1">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B22" s="50" t="str" cm="1">
         <f t="array" ref="B22">INDEX($B$3:$M$3,ROW()-10)</f>
         <v>дек</v>
       </c>
-      <c r="C22" s="53" cm="1">
+      <c r="C22" s="52" cm="1">
         <f t="array" ref="C22">INDEX($B$4:$M$4,ROW()-10)</f>
         <v>65881945</v>
       </c>
-      <c r="D22" s="54">
+      <c r="D22" s="53">
         <f t="shared" si="0"/>
         <v>0.99545535346857839</v>
       </c>
-      <c r="E22" s="55">
+      <c r="E22" s="54">
         <f t="shared" si="1"/>
         <v>8.2954612789048199E-2</v>
       </c>
-      <c r="F22" s="53" cm="1">
+      <c r="F22" s="52" cm="1">
         <f t="array" ref="F22">INDEX($B$5:$M$5,ROW()-10)</f>
         <v>71608529.439999998</v>
       </c>
-      <c r="G22" s="54">
+      <c r="G22" s="53">
         <f t="shared" si="2"/>
         <v>0.96883478719361515</v>
       </c>
-      <c r="H22" s="55">
+      <c r="H22" s="54">
         <f t="shared" si="3"/>
         <v>8.0736232266134592E-2</v>
       </c>
-      <c r="I22" s="53" cm="1">
+      <c r="I22" s="52" cm="1">
         <f t="array" ref="I22">INDEX($B$6:$M$6,ROW()-10)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="54">
+      <c r="J22" s="53">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K22" s="55">
+      <c r="K22" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B23" s="50" t="s">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B23" s="49" t="s">
         <v>1564</v>
       </c>
-      <c r="C23" s="58">
+      <c r="C23" s="57">
         <f>SUM(C11:C22)</f>
         <v>794192664.94000006</v>
       </c>
-      <c r="D23" s="59">
+      <c r="D23" s="58">
         <f>AVERAGE(D11:D22)</f>
         <v>1</v>
       </c>
-      <c r="E23" s="60">
+      <c r="E23" s="59">
         <f>SUM(E11:E22)</f>
         <v>1</v>
       </c>
-      <c r="F23" s="58">
+      <c r="F23" s="57">
         <f>SUM(F11:F22)</f>
         <v>886944156.67000008</v>
       </c>
-      <c r="G23" s="59">
+      <c r="G23" s="58">
         <f>IFERROR(AVERAGE(G11:G22),"")</f>
         <v>0.99999999999999967</v>
       </c>
-      <c r="H23" s="60">
+      <c r="H23" s="59">
         <f>SUM(H11:H22)</f>
         <v>0.99999999999999978</v>
       </c>
-      <c r="I23" s="58">
+      <c r="I23" s="57">
         <f>SUM(I11:I22)</f>
         <v>534666749.24000001</v>
       </c>
-      <c r="J23" s="59">
+      <c r="J23" s="58">
         <f>IFERROR(AVERAGE(J11:J22),"")</f>
         <v>0.75</v>
       </c>
-      <c r="K23" s="60">
+      <c r="K23" s="59">
         <f>SUM(K11:K22)</f>
         <v>1</v>
       </c>
